--- a/ideen.xlsx
+++ b/ideen.xlsx
@@ -483,7 +483,11 @@
           <t>Deutsch</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abgeschlossen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,7 +593,11 @@
           <t>massive western dragon, obsidian-black scales with ember-orange underbelly, four powerful legs, two enormous bat-like wings with red membrane, long spiked tail, glowing amber eyes, smoke trails from nostrils, scarred battle-worn hide, horns swept backwards</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>fake-img-id-123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
